--- a/reports/pdf_change_20260907.xlsx
+++ b/reports/pdf_change_20260907.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,314억   ·   현금 22억(0.5%)      당일 2026-09-07  vs  전영업일 2026-09-04      매수 5종목  /  매도 5종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,482억      당일 2026-09-07  vs  전영업일 2026-09-04      매수 5종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>116</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>442516800</v>
+        <v>441649120</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-24</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-880056000</v>
+        <v>-878330400</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>40</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1315800000</v>
+        <v>1313220000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-14</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1683612000</v>
+        <v>-1680310800</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>39</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>449116200</v>
+        <v>448235580</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-8</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-469200000</v>
+        <v>-468280000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>27</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1330182000</v>
+        <v>1327573800</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-4</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1242360000</v>
+        <v>-1239924000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1238688000</v>
+        <v>1236259200</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-3</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-449208000</v>
+        <v>-448327200</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,530억   ·   현금 44억(1.2%)      당일 2026-09-07  vs  전영업일 2026-09-04      매수 4종목  /  매도 5종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,620억      당일 2026-09-07  vs  전영업일 2026-09-04      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -1176,7 +1176,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,410억   ·   현금 29억(1.2%)      당일 2026-09-07  vs  전영업일 2026-09-04      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,506억      당일 2026-09-07  vs  전영업일 2026-09-04      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1200,7 +1200,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,990억   ·   현금 22억(1.1%)      당일 2026-09-07  vs  전영업일 2026-09-04      매수 3종목  /  매도 2종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,030억      당일 2026-09-07  vs  전영업일 2026-09-04      매수 3종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1296,7 +1296,7 @@
         <v>217</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>2043879600</v>
+        <v>2037760200</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>-285</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-7748466000</v>
+        <v>-7725267000</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>133</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>4086824000</v>
+        <v>4074588000</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>-15</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-136522500</v>
+        <v>-136113750</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>86</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>2050893600</v>
+        <v>2044753200</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 257억   ·   현금 2억(0.6%)      당일 2026-09-07  vs  전영업일 2026-09-04      매수 4종목  /  매도 6종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 267억      당일 2026-09-07  vs  전영업일 2026-09-04      매수 4종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1501,11 +1501,11 @@
         <v>25</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>58100000</v>
+        <v>58887500</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>7.07%→7.30%</t>
+          <t>6.89%→7.13%</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -1522,11 +1522,11 @@
         <v>-52</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-75348000</v>
+        <v>-77714000</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>5.45%→5.16%</t>
+          <t>5.41%→5.12%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
@@ -1545,11 +1545,11 @@
         <v>21</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>71295000</v>
+        <v>70560000</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>1.05%→1.33%</t>
+          <t>1.00%→1.27%</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
@@ -1566,11 +1566,11 @@
         <v>-41</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-27810300</v>
+        <v>-29216600</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>0.92%→0.81%</t>
+          <t>0.93%→0.82%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
@@ -1589,11 +1589,11 @@
         <v>12</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>41622000</v>
+        <v>41916000</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>1.18%→1.35%</t>
+          <t>1.14%→1.30%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
@@ -1610,11 +1610,11 @@
         <v>-18</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-50022000</v>
+        <v>-50148000</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>2.79%→2.59%</t>
+          <t>2.69%→2.50%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
@@ -1633,11 +1633,11 @@
         <v>3</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>87780000</v>
+        <v>93030000</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>0.80%→1.15%</t>
+          <t>0.82%→1.17%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
@@ -1654,11 +1654,11 @@
         <v>-16</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-38528000</v>
+        <v>-44968000</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>3.53%→3.38%</t>
+          <t>3.96%→3.80%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
@@ -1682,11 +1682,11 @@
         <v>-12</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-47628000</v>
+        <v>-49896000</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>1.68%→1.49%</t>
+          <t>1.69%→1.51%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
@@ -1710,11 +1710,11 @@
         <v>-5</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-46970000</v>
+        <v>-47075000</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>0.40%→0.22%</t>
+          <t>0.39%→0.21%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
@@ -1726,7 +1726,7 @@
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 504억   ·   현금 4억(0.8%)      당일 2026-09-07  vs  전영업일 2026-09-04      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 509억      당일 2026-09-07  vs  전영업일 2026-09-04      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B41" s="4" t="n"/>
